--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:23</t>
+    <t xml:space="preserve">2026-09-09 23:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:20</t>
+    <t xml:space="preserve">2026-09-17 14:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:15</t>
+    <t xml:space="preserve">2026-09-23 12:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:44</t>
+    <t xml:space="preserve">2026-10-02 14:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:53</t>
+    <t xml:space="preserve">2026-10-04 09:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:16</t>
+    <t xml:space="preserve">2026-10-05 11:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
